--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>05-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,14 +551,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-118</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>650</v>
+        <v>1450</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>730</v>
+        <v>1530</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>-80</v>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-MAR-26</t>
+          <t>25-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>651</v>
+        <v>1504</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>730</v>
+        <v>1530</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-79</v>
+        <v>-26</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>887</v>
+        <v>1250</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>730</v>
+        <v>1530</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>157</v>
+        <v>-280</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>600</v>
+        <v>1450</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>658</v>
+        <v>1530</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-58</v>
+        <v>-80</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>28-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>600</v>
+        <v>1250</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>658</v>
+        <v>1530</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-58</v>
+        <v>-280</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>07-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>887</v>
+        <v>1250</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>658</v>
+        <v>1830</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>229</v>
+        <v>-580</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>600</v>
+        <v>1450</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>730</v>
+        <v>1830</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-130</v>
+        <v>-380</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>600</v>
+        <v>1450</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>730</v>
+        <v>1830</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-130</v>
+        <v>-380</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11-MAR-26</t>
+          <t>02-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>630</v>
+        <v>1450</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>730</v>
+        <v>1830</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-100</v>
+        <v>-380</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>845</v>
+        <v>1250</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>850</v>
+        <v>1830</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5</v>
+        <v>-580</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>917</v>
+        <v>1250</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>850</v>
+        <v>1830</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>67</v>
+        <v>-580</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>845</v>
+        <v>1250</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>850</v>
+        <v>1830</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5</v>
+        <v>-580</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-MAR-26</t>
+          <t>03-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>845</v>
+        <v>1437</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>850</v>
+        <v>1830</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5</v>
+        <v>-393</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14-MAR-26</t>
+          <t>09-APR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,22 +1140,22 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>917</v>
+        <v>458</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>850</v>
+        <v>460</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>67</v>
+        <v>-2</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>16-APR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1117</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1510</v>
+        <v>460</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-393</v>
+        <v>-39</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-6</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>17-APR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1250</v>
+        <v>421</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1510</v>
+        <v>460</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-260</v>
+        <v>-39</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-6</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>23-APR-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-118</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1450</v>
+        <v>376</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1510</v>
+        <v>460</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-60</v>
+        <v>-84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>24-APR-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1250</v>
+        <v>396</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1510</v>
+        <v>460</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-260</v>
+        <v>-64</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-6</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>30-APR-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,438 +1361,33 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1250</v>
+        <v>376</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1510</v>
+        <v>460</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-260</v>
+        <v>-84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-6</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>19-MAR-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1694</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>1510</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21-MAR-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>651</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>730</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-79</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21-MAR-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>917</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>730</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>25-MAR-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-118</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>28-MAR-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>28-MAR-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>757</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>31-MAR-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>520</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>616</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-96</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>31-MAR-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>616</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,23 +551,23 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1070</v>
+        <v>502</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-120</v>
+        <v>-2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>950</v>
+        <v>651</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1070</v>
+        <v>796</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-120</v>
+        <v>-145</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-118</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>950</v>
+        <v>651</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1070</v>
+        <v>796</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-120</v>
+        <v>-145</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>950</v>
+        <v>745</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1070</v>
+        <v>796</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-120</v>
+        <v>-51</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>950</v>
+        <v>745</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1550</v>
+        <v>796</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-600</v>
+        <v>-51</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>950</v>
+        <v>774</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1550</v>
+        <v>796</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-600</v>
+        <v>-22</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1080</v>
+        <v>600</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1550</v>
+        <v>711</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-470</v>
+        <v>-111</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1080</v>
+        <v>600</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1550</v>
+        <v>711</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-470</v>
+        <v>-111</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1103</v>
+        <v>600</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1550</v>
+        <v>711</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-447</v>
+        <v>-111</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1103</v>
+        <v>600</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1550</v>
+        <v>613</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-447</v>
+        <v>-13</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,40 +991,40 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-326</t>
+          <t>SM-980</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1338</v>
+        <v>745</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1550</v>
+        <v>750</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-212</v>
+        <v>-5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1338</v>
+        <v>600</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1550</v>
+        <v>613</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-212</v>
+        <v>-13</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>845</v>
+        <v>600</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>890</v>
+        <v>613</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-45</v>
+        <v>-13</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>845</v>
+        <v>600</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>890</v>
+        <v>613</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-45</v>
+        <v>-13</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-118</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>600</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>620</v>
+        <v>462</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-20</v>
+        <v>-32</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>620</v>
+        <v>462</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-20</v>
+        <v>123</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>620</v>
+        <v>415</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-20</v>
+        <v>170</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>718</v>
+        <v>400</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>620</v>
+        <v>415</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>98</v>
+        <v>-15</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>718</v>
+        <v>400</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>620</v>
+        <v>415</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>98</v>
+        <v>-15</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10-APR-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>620</v>
+        <v>415</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-44</v>
+        <v>137</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>10-APR-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>576</v>
+        <v>400</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>620</v>
+        <v>462</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-44</v>
+        <v>-62</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10-APR-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>718</v>
+        <v>552</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>620</v>
+        <v>462</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10-APR-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>718</v>
+        <v>500</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>620</v>
+        <v>502</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>600</v>
+        <v>552</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>656</v>
+        <v>462</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-56</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11-APR-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>656</v>
+        <v>462</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-56</v>
+        <v>123</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>14-APR-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>770</v>
+        <v>502</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-25</v>
+        <v>-2</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>14-APR-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>770</v>
+        <v>642</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-25</v>
+        <v>132</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>718</v>
+        <v>600</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>698</v>
+        <v>642</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>20</v>
+        <v>-42</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>718</v>
+        <v>600</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>698</v>
+        <v>792</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>20</v>
+        <v>-192</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>755</v>
+        <v>1250</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>770</v>
+        <v>1872</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-15</v>
+        <v>-622</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>755</v>
+        <v>1250</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>770</v>
+        <v>1872</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-15</v>
+        <v>-622</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>818</v>
+        <v>1258</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>770</v>
+        <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>48</v>
+        <v>-614</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17-APR-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>818</v>
+        <v>1489</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>770</v>
+        <v>1872</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>48</v>
+        <v>-383</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>434</v>
+        <v>1250</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-46</v>
+        <v>-622</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>434</v>
+        <v>1250</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-46</v>
+        <v>-622</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24-APR-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>476</v>
+        <v>1264</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-4</v>
+        <v>-608</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24-APR-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2220,26 +2220,26 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>476</v>
+        <v>1489</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-4</v>
+        <v>-383</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>476</v>
+        <v>1250</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4</v>
+        <v>-622</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>476</v>
+        <v>1250</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-4</v>
+        <v>-622</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01-MAY-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>476</v>
+        <v>1250</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>515</v>
+        <v>1872</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-39</v>
+        <v>-622</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2400,26 +2400,26 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>476</v>
+        <v>627</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>515</v>
+        <v>1872</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-39</v>
+        <v>-1245</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>434</v>
+        <v>1250</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-46</v>
+        <v>-622</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07-MAY-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>434</v>
+        <v>1258</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-46</v>
+        <v>-614</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>10</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>08-MAY-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2535,26 +2535,26 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>434</v>
+        <v>689</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-46</v>
+        <v>-1183</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>08-MAY-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>434</v>
+        <v>1250</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>480</v>
+        <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-46</v>
+        <v>-622</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>476</v>
+        <v>1250</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>590</v>
+        <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-114</v>
+        <v>-622</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>14-MAY-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,30 +2666,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>476</v>
+        <v>1264</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>590</v>
+        <v>1872</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-114</v>
+        <v>-608</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-6</v>
+        <v>10</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>623</v>
+        <v>1250</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>620</v>
+        <v>1872</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>3</v>
+        <v>-622</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>15-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>623</v>
+        <v>1250</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>620</v>
+        <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>3</v>
+        <v>-622</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>16-MAY-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2808,23 +2808,23 @@
         <v>1250</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-300</v>
+        <v>-622</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>16-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,30 +2846,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1250</v>
+        <v>585</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-300</v>
+        <v>-1287</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1250</v>
+        <v>742</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-300</v>
+        <v>-1130</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2940,26 +2940,26 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1250</v>
+        <v>585</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-300</v>
+        <v>-1287</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+        <v>-16</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1250</v>
+        <v>747</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-300</v>
+        <v>-1125</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>30</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>30</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1550</v>
+        <v>1332</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-300</v>
+        <v>-252</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>30</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,28 +3251,28 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1338</v>
+        <v>1080</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-212</v>
+        <v>-792</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3300,24 +3300,24 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1338</v>
+        <v>529</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-212</v>
+        <v>-1343</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3345,26 +3345,26 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1224</v>
+        <v>863</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-326</v>
+        <v>-1009</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1224</v>
+        <v>1080</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-326</v>
+        <v>-792</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>30</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1250</v>
+        <v>552</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-300</v>
+        <v>-1320</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,30 +3476,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1250</v>
+        <v>869</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-300</v>
+        <v>-1003</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>30</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1550</v>
+        <v>1872</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-300</v>
+        <v>-792</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1250</v>
+        <v>585</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1550</v>
+        <v>502</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-300</v>
+        <v>83</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-16</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1338</v>
+        <v>400</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1550</v>
+        <v>462</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-212</v>
+        <v>-62</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1338</v>
+        <v>400</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1550</v>
+        <v>415</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-212</v>
+        <v>-15</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1550</v>
+        <v>415</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-300</v>
+        <v>-15</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>30</v>
@@ -3812,9 +3812,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1550</v>
+        <v>462</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-300</v>
+        <v>-62</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>30</v>
@@ -3857,9 +3857,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1550</v>
+        <v>415</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-300</v>
+        <v>-15</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>30</v>
@@ -3902,9 +3902,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1550</v>
+        <v>415</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-300</v>
+        <v>-15</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>30</v>
@@ -3947,9 +3947,9 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>1550</v>
+        <v>415</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-300</v>
+        <v>-15</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>30</v>
@@ -3992,9 +3992,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1250</v>
+        <v>400</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>1550</v>
+        <v>415</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-300</v>
+        <v>-15</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>30</v>
@@ -4037,9 +4037,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>476</v>
+        <v>400</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>515</v>
+        <v>415</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-39</v>
+        <v>-15</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,2373 +4106,33 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>476</v>
+        <v>400</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>515</v>
+        <v>415</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-39</v>
+        <v>-15</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>29-MAY-26</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>434</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>440</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>29-MAY-26</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>434</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>440</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>-320</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>-320</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>-320</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>-320</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-590</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>534</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>-164</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-590</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>534</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>-164</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>06-JUN-26</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>06-JUN-26</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>13-JUN-26</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>13-JUN-26</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>18-JUN-26</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>18-JUN-26</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>18-JUN-26</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>623</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>18-JUN-26</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>623</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>19-JUN-26</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>19-JUN-26</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>19-JUN-26</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>19-JUN-26</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>19-JUN-26</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>623</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>19-JUN-26</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>623</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>20-JUN-26</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>20-JUN-26</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>480</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>1338</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>-512</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>25-JUN-26</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>1338</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>-512</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>26-JUN-26</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-590</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>-626</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>26-JUN-26</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-590</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>1224</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>-626</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>26-JUN-26</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>26-JUN-26</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>26-JUN-26</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>26-JUN-26</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>27-JUN-26</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>27-JUN-26</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>30-JUN-26</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>30-JUN-26</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
-        </is>
-      </c>
-      <c r="K133" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>500</v>
+        <v>552</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>502</v>
+        <v>613</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2</v>
+        <v>-61</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>796</v>
+        <v>613</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-145</v>
+        <v>-13</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,7 +617,7 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-118</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>796</v>
+        <v>613</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-145</v>
+        <v>-13</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>745</v>
+        <v>600</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>796</v>
+        <v>613</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-51</v>
+        <v>-13</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>745</v>
+        <v>600</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>796</v>
+        <v>613</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-51</v>
+        <v>-13</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>774</v>
+        <v>600</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>796</v>
+        <v>613</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>600</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>711</v>
+        <v>613</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-111</v>
+        <v>-13</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -873,10 +873,10 @@
         <v>600</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>711</v>
+        <v>613</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-111</v>
+        <v>-13</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-118</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>600</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>711</v>
+        <v>613</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-111</v>
+        <v>-13</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>613</v>
+        <v>415</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-13</v>
+        <v>-15</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,38 +991,38 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-980</t>
+          <t>SM-326</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>745</v>
+        <v>552</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>750</v>
+        <v>415</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5</v>
+        <v>137</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,7 +1067,7 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>600</v>
+        <v>552</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-13</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>613</v>
+        <v>502</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1157,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1181,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-118</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>600</v>
+        <v>552</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-13</v>
+        <v>90</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,28 +1226,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>430</v>
+        <v>585</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-32</v>
+        <v>123</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>585</v>
+        <v>500</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>123</v>
+        <v>-2</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>585</v>
+        <v>774</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>415</v>
+        <v>642</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,7 +1337,7 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>415</v>
+        <v>642</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-15</v>
+        <v>-42</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>415</v>
+        <v>792</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-15</v>
+        <v>-192</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>552</v>
+        <v>650</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>415</v>
+        <v>678</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>137</v>
+        <v>-28</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>400</v>
+        <v>1250</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-62</v>
+        <v>-622</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>552</v>
+        <v>1250</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>90</v>
+        <v>-622</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>500</v>
+        <v>1258</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>502</v>
+        <v>1872</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-2</v>
+        <v>-614</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>552</v>
+        <v>1489</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>90</v>
+        <v>-383</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1652,9 +1652,9 @@
       <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>585</v>
+        <v>1250</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>123</v>
+        <v>-622</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>502</v>
+        <v>1872</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2</v>
+        <v>-622</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1742,9 +1742,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>774</v>
+        <v>1250</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>642</v>
+        <v>1872</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>132</v>
+        <v>-622</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>600</v>
+        <v>1264</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>642</v>
+        <v>1872</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-42</v>
+        <v>-608</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>600</v>
+        <v>1489</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>792</v>
+        <v>1872</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-192</v>
+        <v>-383</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-614</v>
+        <v>-622</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1489</v>
+        <v>627</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-383</v>
+        <v>-1245</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-608</v>
+        <v>-614</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>20</v>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1489</v>
+        <v>689</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-383</v>
+        <v>-1183</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>627</v>
+        <v>1250</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1245</v>
+        <v>-622</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-614</v>
+        <v>-622</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>689</v>
+        <v>585</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1183</v>
+        <v>-1287</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1250</v>
+        <v>742</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-622</v>
+        <v>-1130</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-622</v>
+        <v>-792</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>30</v>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1264</v>
+        <v>1080</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-608</v>
+        <v>-792</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1250</v>
+        <v>585</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-622</v>
+        <v>-1287</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-622</v>
+        <v>-792</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>30</v>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-622</v>
+        <v>-792</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>742</v>
+        <v>1080</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1872</v>
+        <v>1332</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-1130</v>
+        <v>-252</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>747</v>
+        <v>529</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1125</v>
+        <v>-1343</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1080</v>
+        <v>572</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-792</v>
+        <v>-1300</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3168,10 +3168,10 @@
         <v>1080</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1332</v>
+        <v>1872</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-252</v>
+        <v>-792</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>30</v>
@@ -3182,9 +3182,9 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1080</v>
+        <v>552</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-792</v>
+        <v>-1320</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,26 +3251,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1080</v>
+        <v>577</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-792</v>
+        <v>-1295</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,26 +3296,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>529</v>
+        <v>1080</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-1343</v>
+        <v>-792</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,26 +3341,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>863</v>
+        <v>1080</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-1009</v>
+        <v>-792</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>552</v>
+        <v>1080</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-1320</v>
+        <v>-792</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,30 +3476,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>869</v>
+        <v>585</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1872</v>
+        <v>502</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-1003</v>
+        <v>83</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1080</v>
+        <v>400</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1872</v>
+        <v>462</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-792</v>
+        <v>-62</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>30</v>
@@ -3542,9 +3542,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1080</v>
+        <v>400</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1872</v>
+        <v>415</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-792</v>
+        <v>-15</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3587,9 +3587,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1080</v>
+        <v>400</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1872</v>
+        <v>415</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-792</v>
+        <v>-15</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3632,9 +3632,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,28 +3656,28 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>83</v>
+        <v>-62</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3708,10 +3708,10 @@
         <v>400</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3722,7 +3722,7 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3843,10 +3843,10 @@
         <v>400</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>30</v>
@@ -3857,7 +3857,7 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -3902,7 +3902,7 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3947,192 +3947,12 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-123</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>613</v>
+        <v>502</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-61</v>
+        <v>-2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>613</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-13</v>
+        <v>-28</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -662,7 +662,7 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -686,7 +686,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -866,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-118</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -932,7 +932,7 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-118</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>415</v>
+        <v>613</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,7 +977,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>552</v>
+        <v>400</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>415</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>137</v>
+        <v>-15</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,28 +1046,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>430</v>
+        <v>552</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-32</v>
+        <v>137</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1091,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>552</v>
+        <v>430</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>90</v>
+        <v>-32</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,28 +1136,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>500</v>
+        <v>552</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1181,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>90</v>
+        <v>-2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>500</v>
+        <v>585</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2</v>
+        <v>123</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1316,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>774</v>
+        <v>500</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>642</v>
+        <v>502</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>132</v>
+        <v>-2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>642</v>
+        <v>678</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-42</v>
+        <v>-28</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1382,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,28 +1406,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>600</v>
+        <v>774</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>792</v>
+        <v>678</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-192</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-28</v>
+        <v>-12</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,7 +1472,7 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1872</v>
+        <v>792</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-622</v>
+        <v>-192</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1250</v>
+        <v>650</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1872</v>
+        <v>678</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-622</v>
+        <v>-28</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-614</v>
+        <v>-622</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1489</v>
+        <v>1250</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-383</v>
+        <v>-622</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-622</v>
+        <v>-614</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1250</v>
+        <v>1489</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-622</v>
+        <v>-383</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1264</v>
+        <v>1250</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-608</v>
+        <v>-622</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
@@ -1856,26 +1856,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1489</v>
+        <v>1250</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-383</v>
+        <v>-622</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1250</v>
+        <v>1489</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-622</v>
+        <v>-383</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>627</v>
+        <v>1250</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1245</v>
+        <v>-622</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1250</v>
+        <v>627</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-622</v>
+        <v>-1245</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-614</v>
+        <v>-622</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>689</v>
+        <v>1258</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1183</v>
+        <v>-614</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1250</v>
+        <v>1264</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-622</v>
+        <v>-608</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>585</v>
+        <v>1250</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1287</v>
+        <v>-622</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>742</v>
+        <v>1250</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1130</v>
+        <v>-622</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-792</v>
+        <v>-1287</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-792</v>
+        <v>-1287</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1332</v>
+        <v>1872</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-252</v>
+        <v>-792</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>30</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1872</v>
+        <v>1332</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-792</v>
+        <v>-252</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
@@ -2957,9 +2957,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>529</v>
+        <v>1080</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1343</v>
+        <v>-792</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>572</v>
+        <v>529</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1300</v>
+        <v>-1343</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
       <c r="I67" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3542,7 +3542,7 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3587,7 +3587,7 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3632,7 +3632,7 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3677,7 +3677,7 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3722,7 +3722,7 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3767,7 +3767,7 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3812,7 +3812,7 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3857,7 +3857,7 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3902,7 +3902,7 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3947,7 +3947,7 @@
       <c r="I77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19-MAY-26</t>
+          <t>22-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>502</v>
+        <v>613</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2</v>
+        <v>-13</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>613</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-28</v>
+        <v>-13</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,27 +631,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-326</t>
+          <t>SM-439</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-231</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>600</v>
+        <v>7990</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>613</v>
+        <v>8102</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-13</v>
+        <v>-112</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,27 +676,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-326</t>
+          <t>SM-433</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-331</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>600</v>
+        <v>7488</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>613</v>
+        <v>9190</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-13</v>
+        <v>-1702</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>613</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-13</v>
+        <v>-72</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-118</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-13</v>
+        <v>-32</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>552</v>
+        <v>430</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>137</v>
+        <v>-32</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>90</v>
+        <v>-2</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>585</v>
+        <v>774</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>462</v>
+        <v>642</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>462</v>
+        <v>612</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>123</v>
+        <v>-12</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>502</v>
+        <v>612</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>678</v>
+        <v>792</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-28</v>
+        <v>-141</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>774</v>
+        <v>1089</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>678</v>
+        <v>912</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>600</v>
+        <v>1089</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>612</v>
+        <v>1872</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-12</v>
+        <v>-783</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1496,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>600</v>
+        <v>1246</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>792</v>
+        <v>1872</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-192</v>
+        <v>-626</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>678</v>
+        <v>1872</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-28</v>
+        <v>-622</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1607,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1250</v>
+        <v>1089</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-622</v>
+        <v>-783</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-614</v>
+        <v>-622</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1489</v>
+        <v>1250</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-383</v>
+        <v>-622</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1832,9 +1832,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1877,9 +1877,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1489</v>
+        <v>1250</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-383</v>
+        <v>-622</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-622</v>
+        <v>-626</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -2057,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>627</v>
+        <v>1250</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1245</v>
+        <v>-622</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2192,9 +2192,9 @@
       <c r="I38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-614</v>
+        <v>-622</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-622</v>
+        <v>-620</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2372,9 +2372,9 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2417,9 +2417,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1264</v>
+        <v>1250</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-608</v>
+        <v>-622</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1250</v>
+        <v>585</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-622</v>
+        <v>-1287</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1250</v>
+        <v>734</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-622</v>
+        <v>-1138</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-622</v>
+        <v>-792</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>30</v>
@@ -2597,9 +2597,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,30 +2666,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-792</v>
+        <v>-1287</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
@@ -2732,9 +2732,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1872</v>
+        <v>1332</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-792</v>
+        <v>-252</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>30</v>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2943,10 +2943,10 @@
         <v>1080</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1332</v>
+        <v>1872</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-252</v>
+        <v>-792</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>30</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1080</v>
+        <v>529</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-792</v>
+        <v>-1343</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1080</v>
+        <v>566</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-792</v>
+        <v>-1306</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3071,30 +3071,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>529</v>
+        <v>1080</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1343</v>
+        <v>-792</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -3137,9 +3137,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,30 +3161,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1080</v>
+        <v>552</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-792</v>
+        <v>-1320</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3206,30 +3206,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1320</v>
+        <v>-1300</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>10</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3251,30 +3251,30 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>577</v>
+        <v>1080</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-1295</v>
+        <v>-792</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3317,9 +3317,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -3362,9 +3362,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -3407,9 +3407,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1872</v>
+        <v>502</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-792</v>
+        <v>83</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,30 +3476,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>83</v>
+        <v>-62</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3528,10 +3528,10 @@
         <v>400</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>30</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3618,10 +3618,10 @@
         <v>400</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-15</v>
+        <v>-62</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3663,10 +3663,10 @@
         <v>400</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>30</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -3904,55 +3904,10 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>651</v>
+        <v>500</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>711</v>
+        <v>516</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-60</v>
+        <v>-16</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,26 +578,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>745</v>
+        <v>552</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>750</v>
+        <v>415</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5</v>
+        <v>137</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>516</v>
+        <v>462</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-16</v>
+        <v>-32</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,17 +668,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>516</v>
+        <v>462</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-16</v>
+        <v>-32</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -695,321 +695,6 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>06-JUN-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>502</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-72</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>430</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-32</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -523,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>500</v>
+        <v>585</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>516</v>
+        <v>415</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>-16</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>552</v>
+        <v>430</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>137</v>
+        <v>-32</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -623,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -668,33 +686,3003 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>430</v>
+        <v>527</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>06-JUN-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>502</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>-32</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-32</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-32</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>12-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>430</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-32</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>774</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>642</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>19-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>612</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>20-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>651</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>792</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-141</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1092</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-142</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1092</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1092</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>26-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-783</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-590</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-590</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-870</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1089</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-783</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>03-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>04-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-590</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-626</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>689</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-1183</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-590</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-870</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>10-JUL-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>11-JUL-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-622</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1287</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-590</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-1138</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1287</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>17-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>18-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1332</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-252</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-1343</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-1320</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-308</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>502</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-62</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-62</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>585</v>
+        <v>430</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>170</v>
+        <v>-32</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>430</v>
+        <v>689</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-32</v>
+        <v>227</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>527</v>
+        <v>430</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65</v>
+        <v>-32</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>430</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-72</v>
+        <v>-32</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>430</v>
+        <v>527</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-32</v>
+        <v>65</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>430</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-32</v>
+        <v>-72</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>774</v>
+        <v>430</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>642</v>
+        <v>462</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>132</v>
+        <v>-32</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-12</v>
+        <v>-32</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>600</v>
+        <v>430</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-12</v>
+        <v>-32</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>792</v>
+        <v>678</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-141</v>
+        <v>-28</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>950</v>
+        <v>774</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1092</v>
+        <v>678</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-142</v>
+        <v>96</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,14 +1181,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1080</v>
+        <v>600</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1092</v>
+        <v>612</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-12</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1089</v>
+        <v>600</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1092</v>
+        <v>612</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1089</v>
+        <v>651</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>912</v>
+        <v>792</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>177</v>
+        <v>-141</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1089</v>
+        <v>650</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1872</v>
+        <v>678</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-783</v>
+        <v>-28</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1246</v>
+        <v>1089</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1872</v>
+        <v>912</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-626</v>
+        <v>177</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1250</v>
+        <v>1089</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1872</v>
+        <v>912</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-622</v>
+        <v>177</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1451,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1250</v>
+        <v>1089</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-622</v>
+        <v>-783</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1002</v>
+        <v>1247</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-870</v>
+        <v>-625</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>20</v>
@@ -1517,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1089</v>
+        <v>1250</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-783</v>
+        <v>-622</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -1607,7 +1607,7 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1631,28 +1631,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1250</v>
+        <v>1002</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-622</v>
+        <v>-870</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1676,28 +1676,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1250</v>
+        <v>1089</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-622</v>
+        <v>-783</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1742,7 +1742,7 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1787,7 +1787,7 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1832,7 +1832,7 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,28 +1856,28 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,28 +1901,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-626</v>
+        <v>-622</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
@@ -1967,7 +1967,7 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1991,28 +1991,28 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,28 +2036,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>689</v>
+        <v>1247</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1183</v>
+        <v>-625</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1002</v>
+        <v>1250</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-870</v>
+        <v>-622</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -2147,7 +2147,7 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1250</v>
+        <v>1002</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-622</v>
+        <v>-870</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2282,7 +2282,7 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2327,7 +2327,7 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2372,7 +2372,7 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,28 +2396,28 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>585</v>
+        <v>1250</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1287</v>
+        <v>-622</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,28 +2441,28 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>734</v>
+        <v>1250</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1138</v>
+        <v>-622</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-792</v>
+        <v>-622</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2507,7 +2507,7 @@
       <c r="I45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2531,28 +2531,28 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-792</v>
+        <v>-1287</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>585</v>
+        <v>735</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1287</v>
+        <v>-1137</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2687,7 +2687,7 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1332</v>
+        <v>1872</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-252</v>
+        <v>-1287</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,28 +2756,28 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1080</v>
+        <v>740</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-792</v>
+        <v>-1132</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2822,7 +2822,7 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,28 +2846,28 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>529</v>
+        <v>1080</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1343</v>
+        <v>-792</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1872</v>
+        <v>1332</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-792</v>
+        <v>-252</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>30</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -2957,7 +2957,7 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,28 +2981,28 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>552</v>
+        <v>1080</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1320</v>
+        <v>-792</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,28 +3026,28 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1080</v>
+        <v>529</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-792</v>
+        <v>-1343</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,28 +3071,28 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1080</v>
+        <v>856</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-792</v>
+        <v>-1016</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
@@ -3137,7 +3137,7 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3210,13 +3210,13 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>502</v>
+        <v>1872</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>83</v>
+        <v>-1320</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3227,9 +3227,9 @@
       <c r="I61" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-62</v>
+        <v>-792</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>30</v>
@@ -3272,9 +3272,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>30</v>
@@ -3317,9 +3317,9 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>30</v>
@@ -3362,9 +3362,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-62</v>
+        <v>-792</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>30</v>
@@ -3407,9 +3407,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>400</v>
+        <v>585</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>415</v>
+        <v>502</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-15</v>
+        <v>83</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3483,10 +3483,10 @@
         <v>400</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-15</v>
+        <v>-62</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
         <v>400</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-15</v>
+        <v>-62</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29-SEP-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3683,6 +3683,231 @@
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>29-SEP-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>689</v>
+        <v>430</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>227</v>
+        <v>-32</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>430</v>
+        <v>527</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-32</v>
+        <v>65</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>430</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-32</v>
+        <v>-72</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>527</v>
+        <v>430</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>65</v>
+        <v>-32</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>430</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-72</v>
+        <v>-32</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>430</v>
+        <v>650</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>462</v>
+        <v>678</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-32</v>
+        <v>-28</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>430</v>
+        <v>774</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>462</v>
+        <v>678</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-32</v>
+        <v>96</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-28</v>
+        <v>-12</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>774</v>
+        <v>600</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>96</v>
+        <v>-12</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>600</v>
+        <v>651</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>612</v>
+        <v>792</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-12</v>
+        <v>-141</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>612</v>
+        <v>678</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-12</v>
+        <v>-28</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>651</v>
+        <v>1089</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>792</v>
+        <v>912</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-141</v>
+        <v>177</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>650</v>
+        <v>1089</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>678</v>
+        <v>912</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-28</v>
+        <v>177</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1368,10 +1368,10 @@
         <v>1089</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>912</v>
+        <v>1872</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>177</v>
+        <v>-783</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1089</v>
+        <v>1247</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>912</v>
+        <v>1872</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>177</v>
+        <v>-625</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1089</v>
+        <v>1250</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-783</v>
+        <v>-622</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-625</v>
+        <v>-622</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1250</v>
+        <v>1002</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-622</v>
+        <v>-870</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1250</v>
+        <v>1089</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-622</v>
+        <v>-783</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1002</v>
+        <v>1250</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-870</v>
+        <v>-622</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1089</v>
+        <v>1250</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-783</v>
+        <v>-622</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-622</v>
+        <v>-625</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-625</v>
+        <v>-622</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1250</v>
+        <v>689</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-622</v>
+        <v>-1183</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1250</v>
+        <v>1002</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-622</v>
+        <v>-870</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1002</v>
+        <v>1250</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-870</v>
+        <v>-622</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1250</v>
+        <v>585</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-622</v>
+        <v>-1287</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1250</v>
+        <v>735</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-622</v>
+        <v>-1137</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>735</v>
+        <v>1080</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1137</v>
+        <v>-792</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-792</v>
+        <v>-1287</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1080</v>
+        <v>740</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-792</v>
+        <v>-1132</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -2711,26 +2711,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>740</v>
+        <v>1080</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-1132</v>
+        <v>-792</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
         <v>1080</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1872</v>
+        <v>1332</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-792</v>
+        <v>-252</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2898,10 +2898,10 @@
         <v>1080</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1332</v>
+        <v>1872</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-252</v>
+        <v>-792</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>30</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1080</v>
+        <v>529</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-792</v>
+        <v>-1343</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,26 +2981,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1080</v>
+        <v>856</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-792</v>
+        <v>-1016</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>529</v>
+        <v>1080</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1343</v>
+        <v>-792</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>856</v>
+        <v>1080</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1016</v>
+        <v>-792</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1080</v>
+        <v>552</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-792</v>
+        <v>-1320</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1080</v>
+        <v>861</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-792</v>
+        <v>-1011</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>552</v>
+        <v>1080</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-1320</v>
+        <v>-792</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1872</v>
+        <v>502</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-792</v>
+        <v>83</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>83</v>
+        <v>-62</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3483,10 +3483,10 @@
         <v>400</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3573,10 +3573,10 @@
         <v>400</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-15</v>
+        <v>-62</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3618,10 +3618,10 @@
         <v>400</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -3863,51 +3863,6 @@
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,36 +541,36 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-326</t>
+          <t>SM-980</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>430</v>
+        <v>784</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>462</v>
+        <v>945</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-32</v>
+        <v>-161</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>527</v>
+        <v>430</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>462</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>65</v>
+        <v>-32</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>430</v>
+        <v>527</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-72</v>
+        <v>65</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -783,10 +783,10 @@
         <v>430</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-32</v>
+        <v>-72</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>650</v>
+        <v>430</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>678</v>
+        <v>462</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-28</v>
+        <v>-32</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>774</v>
+        <v>650</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>678</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>96</v>
+        <v>-28</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>600</v>
+        <v>774</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>612</v>
+        <v>678</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-12</v>
+        <v>96</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>651</v>
+        <v>600</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>792</v>
+        <v>612</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-141</v>
+        <v>-12</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>678</v>
+        <v>792</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-28</v>
+        <v>-141</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1089</v>
+        <v>650</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>912</v>
+        <v>678</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>177</v>
+        <v>-28</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1368,10 +1368,10 @@
         <v>1089</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1872</v>
+        <v>912</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-783</v>
+        <v>177</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1247</v>
+        <v>1089</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-625</v>
+        <v>-783</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-622</v>
+        <v>-626</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1002</v>
+        <v>1250</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-870</v>
+        <v>-622</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1089</v>
+        <v>1002</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-783</v>
+        <v>-870</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1250</v>
+        <v>1089</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-622</v>
+        <v>-783</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1247</v>
+        <v>689</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-625</v>
+        <v>-1183</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-622</v>
+        <v>-626</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1002</v>
+        <v>689</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-870</v>
+        <v>-1183</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2171,26 +2171,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1250</v>
+        <v>1002</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-622</v>
+        <v>-870</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>585</v>
+        <v>1250</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1287</v>
+        <v>-622</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>735</v>
+        <v>585</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1137</v>
+        <v>-1287</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1080</v>
+        <v>734</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-792</v>
+        <v>-1138</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1287</v>
+        <v>-792</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>740</v>
+        <v>585</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1132</v>
+        <v>-1287</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1016</v>
+        <v>-1017</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>40</v>
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>861</v>
+        <v>1080</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-1011</v>
+        <v>-792</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1080</v>
+        <v>585</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1872</v>
+        <v>502</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-792</v>
+        <v>83</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,26 +3386,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>585</v>
+        <v>400</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>83</v>
+        <v>-62</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3438,10 +3438,10 @@
         <v>400</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>30</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>18-AUG-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>25-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3528,10 +3528,10 @@
         <v>400</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>415</v>
+        <v>462</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-15</v>
+        <v>-62</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>30</v>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>01-SEP-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3573,10 +3573,10 @@
         <v>400</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-62</v>
+        <v>-15</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>08-SEP-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>15-SEP-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>29-SEP-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -3818,51 +3818,6 @@
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,36 +541,36 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-980</t>
+          <t>SM-326</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>784</v>
+        <v>319</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>945</v>
+        <v>415</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-161</v>
+        <v>-96</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>30-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-32</v>
+        <v>-18</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-32</v>
+        <v>-18</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-32</v>
+        <v>-15</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>527</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>65</v>
+        <v>-18</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>502</v>
+        <v>415</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-72</v>
+        <v>-18</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-32</v>
+        <v>-18</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-32</v>
+        <v>-15</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-32</v>
+        <v>-18</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>430</v>
+        <v>397</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>462</v>
+        <v>415</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-32</v>
+        <v>-18</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>650</v>
+        <v>397</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>678</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-28</v>
+        <v>-18</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>774</v>
+        <v>397</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>678</v>
+        <v>462</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>96</v>
+        <v>-65</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>600</v>
+        <v>397</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-12</v>
+        <v>-65</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-12</v>
+        <v>-62</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>651</v>
+        <v>397</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>792</v>
+        <v>415</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-141</v>
+        <v>-18</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>650</v>
+        <v>400</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>678</v>
+        <v>415</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-28</v>
+        <v>-15</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1089</v>
+        <v>430</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>912</v>
+        <v>462</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>177</v>
+        <v>-32</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1089</v>
+        <v>430</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>912</v>
+        <v>462</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>177</v>
+        <v>-32</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1089</v>
+        <v>600</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1872</v>
+        <v>678</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-783</v>
+        <v>-78</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1246</v>
+        <v>600</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1872</v>
+        <v>678</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-626</v>
+        <v>-78</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1872</v>
+        <v>612</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-622</v>
+        <v>-12</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1872</v>
+        <v>612</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-622</v>
+        <v>-12</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1002</v>
+        <v>600</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1872</v>
+        <v>612</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-870</v>
+        <v>-12</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>20-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1089</v>
+        <v>600</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1872</v>
+        <v>792</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-783</v>
+        <v>-192</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1250</v>
+        <v>650</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1872</v>
+        <v>678</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-622</v>
+        <v>-28</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1697,9 +1697,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1250</v>
+        <v>651</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1872</v>
+        <v>678</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-622</v>
+        <v>-27</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30</v>
@@ -1742,9 +1742,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1250</v>
+        <v>845</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1872</v>
+        <v>912</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-622</v>
+        <v>-67</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1250</v>
+        <v>845</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1872</v>
+        <v>912</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-622</v>
+        <v>-67</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1832,9 +1832,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1250</v>
+        <v>845</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1872</v>
+        <v>1092</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-622</v>
+        <v>-247</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>30</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1905,13 +1905,13 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1250</v>
+        <v>950</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1872</v>
+        <v>1092</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-622</v>
+        <v>-142</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>30</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>689</v>
+        <v>845</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1872</v>
+        <v>912</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1183</v>
+        <v>-67</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,28 +1991,28 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1246</v>
+        <v>972</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-626</v>
+        <v>-900</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,28 +2036,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-622</v>
+        <v>-624</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -2102,7 +2102,7 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2126,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>689</v>
+        <v>1250</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1183</v>
+        <v>-622</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2171,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1002</v>
+        <v>972</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-870</v>
+        <v>-900</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1250</v>
+        <v>1003</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-622</v>
+        <v>-869</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -2282,7 +2282,7 @@
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -2327,7 +2327,7 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2372,7 +2372,7 @@
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>04-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2417,7 +2417,7 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2462,7 +2462,7 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,28 +2486,28 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>585</v>
+        <v>1250</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1287</v>
+        <v>-622</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,28 +2531,28 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>734</v>
+        <v>462</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1138</v>
+        <v>-1410</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1080</v>
+        <v>1248</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-792</v>
+        <v>-624</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-792</v>
+        <v>-622</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>30</v>
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,28 +2666,28 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>585</v>
+        <v>1250</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1287</v>
+        <v>-622</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,28 +2711,28 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1080</v>
+        <v>480</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-792</v>
+        <v>-1392</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>17-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,28 +2756,28 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1080</v>
+        <v>1003</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-792</v>
+        <v>-869</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>18-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1332</v>
+        <v>1872</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-252</v>
+        <v>-622</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-792</v>
+        <v>-622</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>30</v>
@@ -2867,7 +2867,7 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-792</v>
+        <v>-622</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>30</v>
@@ -2912,7 +2912,7 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,28 +2936,28 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>529</v>
+        <v>1250</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-1343</v>
+        <v>-622</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,28 +2981,28 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nesma Airlines NE-121</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>855</v>
+        <v>1250</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1017</v>
+        <v>-622</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-792</v>
+        <v>-622</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>30</v>
@@ -3047,7 +3047,7 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,28 +3071,28 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1080</v>
+        <v>444</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-792</v>
+        <v>-1428</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,28 +3116,28 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>552</v>
+        <v>735</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-1320</v>
+        <v>-1137</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
@@ -3227,7 +3227,7 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>24-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,28 +3251,28 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1080</v>
+        <v>444</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1872</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-792</v>
+        <v>-1428</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3317,7 +3317,7 @@
       <c r="I63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>585</v>
+        <v>1080</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>502</v>
+        <v>1872</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>83</v>
+        <v>-792</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>462</v>
+        <v>1332</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-62</v>
+        <v>-252</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>30</v>
@@ -3407,9 +3407,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>30</v>
@@ -3452,9 +3452,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>18-AUG-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3497,9 +3497,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>25-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>462</v>
+        <v>1872</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-62</v>
+        <v>-1464</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>01-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3587,9 +3587,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3632,9 +3632,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-15</v>
+        <v>-1452</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3722,9 +3722,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>400</v>
+        <v>1080</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>415</v>
+        <v>1872</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-15</v>
+        <v>-792</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>30</v>
@@ -3767,9 +3767,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,43 +3781,628 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>24-JUL-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-108</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>25-JUL-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-208</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-792</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>31-JUL-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>444</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>502</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-58</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-62</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>18-AUG-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>25-AUG-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-62</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>01-SEP-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>08-SEP-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>15-SEP-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-121</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-123</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-812</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>462</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>415</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
           <t>29-SEP-26</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-326</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Nesma Airlines NE-121</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n">
+      <c r="D87" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E87" s="2" t="n">
         <v>415</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F87" s="2" t="n">
         <v>-15</v>
       </c>
-      <c r="G74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="G87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>319</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-96</v>
+        <v>-43</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-18</v>
+        <v>-83</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>06-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>400</v>
+        <v>319</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-15</v>
+        <v>4</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -735,22 +735,22 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>12-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -825,22 +825,22 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-18</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>13-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>400</v>
+        <v>319</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>415</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-15</v>
+        <v>4</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>05-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-14</v>
+        <v>35</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>397</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>415</v>
+        <v>542</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-18</v>
+        <v>-42</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>397</v>
+        <v>500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>415</v>
+        <v>542</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-18</v>
+        <v>-42</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>19-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>397</v>
+        <v>500</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>415</v>
+        <v>542</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-18</v>
+        <v>-42</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>397</v>
+        <v>732</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>462</v>
+        <v>542</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-65</v>
+        <v>190</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>26-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>397</v>
+        <v>732</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>462</v>
+        <v>542</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-65</v>
+        <v>190</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12-JUN-26</t>
+          <t>27-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>462</v>
+        <v>437</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-62</v>
+        <v>-7</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>397</v>
+        <v>732</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>415</v>
+        <v>542</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-18</v>
+        <v>190</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>03-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>400</v>
+        <v>732</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>415</v>
+        <v>620</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-15</v>
+        <v>112</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>430</v>
+        <v>732</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>462</v>
+        <v>620</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-32</v>
+        <v>112</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>430</v>
+        <v>732</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>462</v>
+        <v>1772</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-32</v>
+        <v>-1040</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>678</v>
+        <v>1772</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-78</v>
+        <v>-822</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1427,9 +1427,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>678</v>
+        <v>1772</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-78</v>
+        <v>-822</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>10-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1496,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>600</v>
+        <v>1003</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>612</v>
+        <v>1772</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-12</v>
+        <v>-769</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>11-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>612</v>
+        <v>1772</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-12</v>
+        <v>-822</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1562,9 +1562,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19-JUN-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>612</v>
+        <v>1772</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-12</v>
+        <v>-822</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1607,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20-JUN-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>600</v>
+        <v>1250</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>792</v>
+        <v>1772</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-192</v>
+        <v>-522</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1652,9 +1652,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>650</v>
+        <v>416</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>678</v>
+        <v>1772</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-28</v>
+        <v>-1356</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>651</v>
+        <v>735</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>678</v>
+        <v>1772</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-27</v>
+        <v>-1037</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>845</v>
+        <v>745</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>912</v>
+        <v>1772</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-67</v>
+        <v>-1027</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>26-JUN-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>845</v>
+        <v>1080</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>912</v>
+        <v>1772</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-67</v>
+        <v>-692</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1832,9 +1832,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>845</v>
+        <v>416</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1092</v>
+        <v>1772</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-247</v>
+        <v>-1356</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>950</v>
+        <v>741</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1092</v>
+        <v>1772</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-142</v>
+        <v>-1031</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>845</v>
+        <v>745</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>912</v>
+        <v>1772</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-67</v>
+        <v>-1027</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>30</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>17-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,26 +1991,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>972</v>
+        <v>745</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-900</v>
+        <v>-1027</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>18-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,26 +2036,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1248</v>
+        <v>745</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1872</v>
+        <v>1232</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-624</v>
+        <v>-487</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-622</v>
+        <v>-1272</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>30</v>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-622</v>
+        <v>-692</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>30</v>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>972</v>
+        <v>394</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-900</v>
+        <v>-1378</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1003</v>
+        <v>500</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-869</v>
+        <v>-1272</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1250</v>
+        <v>856</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-622</v>
+        <v>-916</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>Nesma Airlines NE-123</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1250</v>
+        <v>1080</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-622</v>
+        <v>-692</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>30</v>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>03-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,26 +2351,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-108</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1250</v>
+        <v>408</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-622</v>
+        <v>-1364</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-622</v>
+        <v>-1272</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>30</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1250</v>
+        <v>500</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-622</v>
+        <v>-1272</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>30</v>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>24-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Air Arabia Egypt E5-590</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1250</v>
+        <v>572</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-622</v>
+        <v>-1200</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>462</v>
+        <v>500</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1872</v>
+        <v>1772</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1410</v>
+        <v>-1272</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1248</v>
+        <v>397</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1872</v>
+        <v>402</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-624</v>
+        <v>-5</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-123</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1250</v>
+        <v>397</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1872</v>
+        <v>402</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-622</v>
+        <v>-5</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>30</v>
@@ -2642,9 +2642,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-208</t>
+          <t>Nile Air NP-308</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1250</v>
+        <v>397</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1872</v>
+        <v>402</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-622</v>
+        <v>-5</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>30</v>
@@ -2687,9 +2687,9 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-812</t>
+          <t>Nile Air NP-108</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>480</v>
+        <v>397</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1872</v>
+        <v>402</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1392</v>
+        <v>-5</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>31-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-590</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1003</v>
+        <v>416</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1872</v>
+        <v>402</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-869</v>
+        <v>14</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-121</t>
+          <t>Nile Air NP-208</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1250</v>
+        <v>397</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1872</v>
+        <v>437</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-622</v>
+        <v>-40</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>10-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,1563 +2846,33 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-308</t>
+          <t>EgyptAir MS-812</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1250</v>
+        <v>462</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1872</v>
+        <v>315</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-622</v>
+        <v>147</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>10-JUL-26</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>-622</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>11-JUL-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>-622</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>14-JUL-26</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>-622</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>14-JUL-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-622</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>16-JUL-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-1428</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>16-JUL-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-590</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>735</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>-1137</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>16-JUL-26</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-123</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>16-JUL-26</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>-1428</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>17-JUL-26</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>18-JUL-26</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>1332</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>-252</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>21-JUL-26</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>21-JUL-26</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E67" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>408</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>-1464</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-123</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="n">
-        <v>420</v>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>-1452</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E72" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F72" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-308</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H73" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>24-JUL-26</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-108</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>25-JUL-26</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-208</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>-792</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>444</v>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>502</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>-58</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>04-AUG-26</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>-62</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>11-AUG-26</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>18-AUG-26</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>25-AUG-26</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>-62</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>01-SEP-26</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>08-SEP-26</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>15-SEP-26</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-123</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-812</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>462</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>29-SEP-26</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SM-326</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-121</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>415</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
